--- a/.qoder/skills/combo-stability-writer/组合稳定性分布_指标计算器 （发版前）.xlsx
+++ b/.qoder/skills/combo-stability-writer/组合稳定性分布_指标计算器 （发版前）.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>组合稳定性分布图 — 指标计算器(基于需求口径)</t>
   </si>
@@ -238,6 +238,9 @@
 6. σ为总体标准差STDEV.P；μ/σ仅统计有效天(B列非空;参与天数=T)；LCB(悲观排名)=μ+z·σ/√T(z=B3=1)，越小越好(对齐前端879行)。
 7. 修改B2(组合总数)、B3(z)、B4(区间天数D)后所有指标自动重算；数据区最多31行。
 8. 本表A-D列取自真实报文组合“太乙-七天前实际负荷 × 综合模型”(2026-07-21~2026-08-20)，C/D列=报文原值÷10000(单位:万)；B列每日排名按requirement口径计算(当日收益降序、并列按报文顺序取相邻名次)；报文基准validDays=28/winDays=17/winRate=0.6071/coverage=0.9032</t>
+  </si>
+  <si>
+    <t>前10% → 稳定优秀（绿）｜前35% → 较稳定（浅绿）｜中部 → 表现中等（橙）｜后35% → 不稳定（浅红）｜后10% → 易爆雷（红）</t>
   </si>
 </sst>
 </file>
@@ -1294,7 +1297,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="55.25" customWidth="1"/>
@@ -2053,6 +2056,12 @@
         <v>67</v>
       </c>
     </row>
+    <row r="59" ht="93" customHeight="1"/>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:E1"/>
